--- a/src/test/resources/testdata/test-data.xlsx
+++ b/src/test/resources/testdata/test-data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Future_LocalDiskD\Test-automation\enterprise-automation-framework\src\test\resources\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CF5668B-3B93-4DA1-ABDE-3EF6A060999F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBE092CE-4C8E-4394-888D-6FA43BDEEDCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{0F24B6FF-4DC8-4C0E-83FA-62EF3AAD6ED8}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="33">
   <si>
     <t>TestCase</t>
   </si>
@@ -72,46 +72,70 @@
     <t>Failure</t>
   </si>
   <si>
-    <t>FirstName</t>
-  </si>
-  <si>
-    <t>MiddleName</t>
-  </si>
-  <si>
-    <t>LastName</t>
-  </si>
-  <si>
-    <t>EmployeeId</t>
-  </si>
-  <si>
     <t>TC_EMP_001</t>
   </si>
   <si>
     <t>John</t>
   </si>
   <si>
-    <t>A</t>
-  </si>
-  <si>
     <t>Smith</t>
   </si>
   <si>
-    <t>EMP001</t>
-  </si>
-  <si>
     <t>TC_EMP_002</t>
   </si>
   <si>
     <t>Rahul</t>
   </si>
   <si>
-    <t>K</t>
-  </si>
-  <si>
     <t>Patil</t>
   </si>
   <si>
-    <t>EMP002</t>
+    <t>Test Case</t>
+  </si>
+  <si>
+    <t>First Name</t>
+  </si>
+  <si>
+    <t>Middle Name</t>
+  </si>
+  <si>
+    <t>Last Name</t>
+  </si>
+  <si>
+    <t>Employee ID</t>
+  </si>
+  <si>
+    <t>Expected Result</t>
+  </si>
+  <si>
+    <t>Michael</t>
+  </si>
+  <si>
+    <t>Kumar</t>
+  </si>
+  <si>
+    <t>TC_EMP_003</t>
+  </si>
+  <si>
+    <t>Amit</t>
+  </si>
+  <si>
+    <t>Raj</t>
+  </si>
+  <si>
+    <t>Sharma</t>
+  </si>
+  <si>
+    <t>TC_EMP_004</t>
+  </si>
+  <si>
+    <t>Priya</t>
+  </si>
+  <si>
+    <t>Suresh</t>
+  </si>
+  <si>
+    <t>Deshmukh</t>
   </si>
 </sst>
 </file>
@@ -549,58 +573,110 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE9C618A-022C-4BA0-A8FE-A9E74958C19A}">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.88671875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="C2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E2" s="2">
+        <v>1001</v>
+      </c>
+      <c r="F2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="B3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>24</v>
+      <c r="E3" s="2">
+        <v>1002</v>
+      </c>
+      <c r="F3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4">
+        <v>1003</v>
+      </c>
+      <c r="F4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5">
+        <v>1004</v>
+      </c>
+      <c r="F5" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
